--- a/template_nara.xlsx
+++ b/template_nara.xlsx
@@ -1815,8 +1815,9 @@
           <t xml:space="preserve">Personnel Costs </t>
         </is>
       </c>
-      <c r="D24" s="83" t="n">
-        <v>86374120</v>
+      <c r="D24" s="83">
+        <f>D43+D66+D69+D72</f>
+        <v/>
       </c>
       <c r="E24" s="84">
         <f>D24/D$31</f>
@@ -1824,7 +1825,7 @@
       </c>
       <c r="F24" s="85" t="n"/>
       <c r="G24" s="86">
-        <f>D24</f>
+        <f>G43+G66+G69+G72</f>
         <v/>
       </c>
       <c r="H24" s="84">
@@ -1833,7 +1834,7 @@
       </c>
       <c r="I24" s="85" t="n"/>
       <c r="J24" s="86">
-        <f>G24</f>
+        <f>J43+J66+J69+J72</f>
         <v/>
       </c>
       <c r="K24" s="84">
@@ -1842,7 +1843,7 @@
       </c>
       <c r="L24" s="85" t="n"/>
       <c r="M24" s="86">
-        <f>J24</f>
+        <f>M43+M66+M69+M72</f>
         <v/>
       </c>
       <c r="N24" s="84">
@@ -1851,7 +1852,7 @@
       </c>
       <c r="O24" s="85" t="n"/>
       <c r="P24" s="86">
-        <f>M24</f>
+        <f>P43+P66+P69+P72</f>
         <v/>
       </c>
       <c r="Q24" s="87">
@@ -3911,52 +3912,56 @@
           <t xml:space="preserve">  Other </t>
         </is>
       </c>
-      <c r="D67" s="101">
-        <f>E67*D31</f>
-        <v/>
-      </c>
-      <c r="E67" s="124" t="n">
-        <v>0.04151456599440539</v>
+      <c r="D67" s="101" t="n">
+        <v>40543678.66679813</v>
+      </c>
+      <c r="E67" s="124">
+        <f>D67/D$31</f>
+        <v/>
       </c>
       <c r="F67" s="77" t="n">
         <v>0</v>
       </c>
       <c r="G67" s="184">
-        <f>H67*G31</f>
-        <v/>
-      </c>
-      <c r="H67" s="124" t="n">
-        <v>0.03883554889853111</v>
+        <f>D67*(1+F67)</f>
+        <v/>
+      </c>
+      <c r="H67" s="124">
+        <f>G67/G$31</f>
+        <v/>
       </c>
       <c r="I67" s="77" t="n">
         <v>0</v>
       </c>
       <c r="J67" s="184">
-        <f>K67*J31</f>
-        <v/>
-      </c>
-      <c r="K67" s="124" t="n">
-        <v>0.03675772796817611</v>
+        <f>G67*(1+I67)</f>
+        <v/>
+      </c>
+      <c r="K67" s="124">
+        <f>J67/J$31</f>
+        <v/>
       </c>
       <c r="L67" s="77" t="n">
         <v>0.01</v>
       </c>
       <c r="M67" s="184">
-        <f>N67*M31</f>
-        <v/>
-      </c>
-      <c r="N67" s="124" t="n">
-        <v>0.03571900973750043</v>
+        <f>J67*(1+L67)</f>
+        <v/>
+      </c>
+      <c r="N67" s="124">
+        <f>M67/M$31</f>
+        <v/>
       </c>
       <c r="O67" s="77" t="n">
         <v>0.01</v>
       </c>
       <c r="P67" s="184">
-        <f>Q67*P31</f>
-        <v/>
-      </c>
-      <c r="Q67" s="125" t="n">
-        <v>0.0349374248885173</v>
+        <f>M67*(1+O67)</f>
+        <v/>
+      </c>
+      <c r="Q67" s="125">
+        <f>P67/P$31</f>
+        <v/>
       </c>
       <c r="S67" s="35" t="n"/>
       <c r="T67" s="66" t="n"/>
@@ -4080,12 +4085,12 @@
           <t xml:space="preserve">  Other </t>
         </is>
       </c>
-      <c r="D70" s="101">
-        <f>E70*D31</f>
-        <v/>
-      </c>
-      <c r="E70" s="124" t="n">
-        <v>0.019522514669497</v>
+      <c r="D70" s="101" t="n">
+        <v>19065948.12130773</v>
+      </c>
+      <c r="E70" s="124">
+        <f>D70/D$31</f>
+        <v/>
       </c>
       <c r="F70" s="144" t="inlineStr">
         <is>
@@ -4254,52 +4259,56 @@
           <t xml:space="preserve">  Other </t>
         </is>
       </c>
-      <c r="D73" s="101">
-        <f>E73*D31</f>
-        <v/>
-      </c>
-      <c r="E73" s="124" t="n">
-        <v>0.02631966325897113</v>
+      <c r="D73" s="101" t="n">
+        <v>25704134.06065387</v>
+      </c>
+      <c r="E73" s="124">
+        <f>D73/D$31</f>
+        <v/>
       </c>
       <c r="F73" s="77" t="n">
         <v>0</v>
       </c>
       <c r="G73" s="184">
-        <f>H73*G31</f>
-        <v/>
-      </c>
-      <c r="H73" s="124" t="n">
-        <v>0.02462120330547095</v>
+        <f>D73*(1+F73)</f>
+        <v/>
+      </c>
+      <c r="H73" s="124">
+        <f>G73/G$31</f>
+        <v/>
       </c>
       <c r="I73" s="77" t="n">
         <v>0</v>
       </c>
       <c r="J73" s="184">
-        <f>K73*J31</f>
-        <v/>
-      </c>
-      <c r="K73" s="124" t="n">
-        <v>0.02330389344351176</v>
+        <f>G73*(1+I73)</f>
+        <v/>
+      </c>
+      <c r="K73" s="124">
+        <f>J73/J$31</f>
+        <v/>
       </c>
       <c r="L73" s="77" t="n">
         <v>0.01</v>
       </c>
       <c r="M73" s="184">
-        <f>N73*M31</f>
-        <v/>
-      </c>
-      <c r="N73" s="124" t="n">
-        <v>0.0226453603865596</v>
+        <f>J73*(1+L73)</f>
+        <v/>
+      </c>
+      <c r="N73" s="124">
+        <f>M73/M$31</f>
+        <v/>
       </c>
       <c r="O73" s="77" t="n">
         <v>0.01</v>
       </c>
       <c r="P73" s="184">
-        <f>Q73*P31</f>
-        <v/>
-      </c>
-      <c r="Q73" s="125" t="n">
-        <v>0.02214984635333276</v>
+        <f>M73*(1+O73)</f>
+        <v/>
+      </c>
+      <c r="Q73" s="125">
+        <f>P73/P$31</f>
+        <v/>
       </c>
     </row>
     <row r="74" ht="13" customHeight="1">
